--- a/Result/profitability/5490.xlsx
+++ b/Result/profitability/5490.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.19</v>
       </c>
       <c r="M2" t="n">
-        <v>0.305</v>
+        <v>0.37875</v>
       </c>
       <c r="N2" t="n">
-        <v>39.63</v>
+        <v>40.82125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.64</v>
       </c>
       <c r="M3" t="n">
-        <v>0.385</v>
+        <v>0.43</v>
       </c>
       <c r="N3" t="n">
-        <v>38.80375</v>
+        <v>39.6175</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.27</v>
       </c>
       <c r="M4" t="n">
-        <v>0.39</v>
+        <v>0.3700000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>38.04875</v>
+        <v>37.6175</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.82</v>
       </c>
       <c r="M5" t="n">
-        <v>0.39875</v>
+        <v>0.45875</v>
       </c>
       <c r="N5" t="n">
-        <v>35.955</v>
+        <v>35.4075</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.51</v>
       </c>
       <c r="M6" t="n">
-        <v>0.32125</v>
+        <v>0.345</v>
       </c>
       <c r="N6" t="n">
-        <v>31.68375</v>
+        <v>31.68625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.7</v>
       </c>
       <c r="M7" t="n">
-        <v>0.35875</v>
+        <v>0.3775</v>
       </c>
       <c r="N7" t="n">
-        <v>30.23375</v>
+        <v>30.67875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.34</v>
       </c>
       <c r="M8" t="n">
-        <v>0.34625</v>
+        <v>0.3325000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>29.0675</v>
+        <v>28.8</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.18</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4037500000000001</v>
+        <v>0.40375</v>
       </c>
       <c r="N10" t="n">
         <v>26.88625</v>
@@ -2026,7 +2026,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6299999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="N13" t="n">
         <v>28.995</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5490</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>459</v>
+      </c>
+      <c r="D75" t="n">
+        <v>263</v>
+      </c>
+      <c r="E75" t="n">
+        <v>195</v>
+      </c>
+      <c r="F75" t="n">
+        <v>42.57</v>
+      </c>
+      <c r="G75" t="n">
+        <v>66</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>14.48%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>67</v>
+      </c>
+      <c r="K75" t="n">
+        <v>55</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="N75" t="n">
+        <v>41.36375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1571428571428571</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.140000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.04786401252516215</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>4.363636363636363</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.380000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.09329073482428119</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
